--- a/cet4/result/65_侦探女神_真相追踪的逆袭/65_侦探女神_真相追踪的逆袭_学习版.xlsx
+++ b/cet4/result/65_侦探女神_真相追踪的逆袭/65_侦探女神_真相追踪的逆袭_学习版.xlsx
@@ -397,1067 +397,689 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D48"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>notebook</v>
       </c>
       <c r="B2" t="str">
-        <v>notebook</v>
+        <v>/ˈnoʊtbʊk/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>笔记本</v>
       </c>
-      <c r="D2" t="str">
-        <v>notebook(笔记本)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>occupation</v>
       </c>
       <c r="B3" t="str">
-        <v>occupation</v>
+        <v>/ˌɑːkjuˈpeɪʃn/</v>
       </c>
       <c r="C3" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D3" t="str">
         <v>职业</v>
       </c>
-      <c r="D3" t="str">
-        <v>occupation(职业)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>suburb</v>
       </c>
       <c r="B4" t="str">
-        <v>suburb</v>
+        <v>/ˈsʌbɜːrb/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>郊区</v>
       </c>
-      <c r="D4" t="str">
-        <v>suburb(郊区)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>small</v>
       </c>
       <c r="B5" t="str">
-        <v>small</v>
+        <v>/smɔːl/</v>
       </c>
       <c r="C5" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D5" t="str">
         <v>小的</v>
       </c>
-      <c r="D5" t="str">
-        <v>small(小的)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>former</v>
       </c>
       <c r="B6" t="str">
-        <v>former</v>
+        <v>/ˈfɔːrmər/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D6" t="str">
         <v>以前的</v>
       </c>
-      <c r="D6" t="str">
-        <v>former(以前的)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>child</v>
       </c>
       <c r="B7" t="str">
-        <v>child</v>
+        <v>/tʃaɪld/</v>
       </c>
       <c r="C7" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D7" t="str">
         <v>孩子</v>
       </c>
-      <c r="D7" t="str">
-        <v>child(孩子)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>average</v>
       </c>
       <c r="B8" t="str">
-        <v>average</v>
+        <v>/ˈævərɪdʒ/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D8" t="str">
         <v>普通的</v>
       </c>
-      <c r="D8" t="str">
-        <v>average(普通的)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>lose</v>
       </c>
       <c r="B9" t="str">
-        <v>lose</v>
+        <v>/luːz/</v>
       </c>
       <c r="C9" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D9" t="str">
         <v>失去</v>
       </c>
-      <c r="D9" t="str">
-        <v>lose(失去)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>charity</v>
       </c>
       <c r="B10" t="str">
-        <v>charity</v>
+        <v>/ˈtʃærəti/</v>
       </c>
       <c r="C10" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D10" t="str">
         <v>慈善</v>
       </c>
-      <c r="D10" t="str">
-        <v>charity(慈善)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>accept</v>
       </c>
       <c r="B11" t="str">
-        <v>accept</v>
+        <v>/əkˈsept/</v>
       </c>
       <c r="C11" t="str">
+        <v>vt./vi.</v>
+      </c>
+      <c r="D11" t="str">
         <v>接受</v>
       </c>
-      <c r="D11" t="str">
-        <v>accept(接受)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>highway</v>
       </c>
       <c r="B12" t="str">
-        <v>highway</v>
+        <v>/ˈhaɪweɪ/</v>
       </c>
       <c r="C12" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D12" t="str">
         <v>公路</v>
       </c>
-      <c r="D12" t="str">
-        <v>highway(公路)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>photographic</v>
       </c>
       <c r="B13" t="str">
-        <v>photographic</v>
+        <v>/ˌfoʊtəˈɡræfɪk/</v>
       </c>
       <c r="C13" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D13" t="str">
         <v>摄影的</v>
       </c>
-      <c r="D13" t="str">
-        <v>photographic(摄影的)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>cave</v>
       </c>
       <c r="B14" t="str">
-        <v>cave</v>
+        <v>/keɪv/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./v./int.</v>
+      </c>
+      <c r="D14" t="str">
         <v>洞穴</v>
       </c>
-      <c r="D14" t="str">
-        <v>cave(洞穴)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>greenhouse</v>
       </c>
       <c r="B15" t="str">
-        <v>greenhouse</v>
+        <v>/ˈɡriːnhaʊs/</v>
       </c>
       <c r="C15" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D15" t="str">
         <v>温室</v>
       </c>
-      <c r="D15" t="str">
-        <v>greenhouse(温室)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>card</v>
       </c>
       <c r="B16" t="str">
-        <v>child</v>
+        <v>/kɑːrd/</v>
       </c>
       <c r="C16" t="str">
-        <v>孩子</v>
+        <v>n./vt.</v>
       </c>
       <c r="D16" t="str">
-        <v>child(孩子)📢</v>
+        <v>卡片</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>origin</v>
       </c>
       <c r="B17" t="str">
-        <v>small</v>
+        <v>/ˈɔːrɪdʒɪn/</v>
       </c>
       <c r="C17" t="str">
-        <v>小的</v>
+        <v>n.</v>
       </c>
       <c r="D17" t="str">
-        <v>small(小的)📢</v>
+        <v>起源</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>agency</v>
       </c>
       <c r="B18" t="str">
-        <v>card</v>
+        <v>/ˈeɪdʒənsi/</v>
       </c>
       <c r="C18" t="str">
-        <v>卡片</v>
+        <v>n.</v>
       </c>
       <c r="D18" t="str">
-        <v>card(卡片)📢</v>
+        <v>代理</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>mean</v>
       </c>
       <c r="B19" t="str">
-        <v>origin</v>
+        <v>/miːn/</v>
       </c>
       <c r="C19" t="str">
-        <v>起源</v>
+        <v>n./vt./vi./adj.</v>
       </c>
       <c r="D19" t="str">
-        <v>origin(起源)📢</v>
+        <v>意谓</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>Indian</v>
       </c>
       <c r="B20" t="str">
-        <v>origin</v>
+        <v>/ˈɪndiən/</v>
       </c>
       <c r="C20" t="str">
-        <v>起源</v>
+        <v>n./adj.</v>
       </c>
       <c r="D20" t="str">
-        <v>origin(起源)📢</v>
+        <v>印度</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>issue</v>
       </c>
       <c r="B21" t="str">
-        <v>notebook</v>
+        <v>/ˈɪʃuː/</v>
       </c>
       <c r="C21" t="str">
-        <v>笔记本</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D21" t="str">
-        <v>notebook(笔记本)📢</v>
+        <v>发布</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>auto</v>
       </c>
       <c r="B22" t="str">
-        <v>agency</v>
+        <v>/ˈɔːtoʊ/</v>
       </c>
       <c r="C22" t="str">
-        <v>代理</v>
+        <v>n./vi.</v>
       </c>
       <c r="D22" t="str">
-        <v>agency(代理)📢</v>
+        <v>汽车</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>foolish</v>
       </c>
       <c r="B23" t="str">
-        <v>mean</v>
+        <v>/ˈfuːlɪʃ/</v>
       </c>
       <c r="C23" t="str">
-        <v>意谓</v>
+        <v>adj.</v>
       </c>
       <c r="D23" t="str">
-        <v>mean(意谓)📢</v>
+        <v>愚蠢的</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>folk</v>
       </c>
       <c r="B24" t="str">
-        <v>Indian</v>
+        <v>/foʊk/</v>
       </c>
       <c r="C24" t="str">
-        <v>印度</v>
+        <v>n./adj.</v>
       </c>
       <c r="D24" t="str">
-        <v>Indian(印度)📢</v>
+        <v>民间</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>judge</v>
       </c>
       <c r="B25" t="str">
-        <v>average</v>
+        <v>/dʒʌdʒ/</v>
       </c>
       <c r="C25" t="str">
-        <v>普通的</v>
+        <v>n./v.</v>
       </c>
       <c r="D25" t="str">
-        <v>average(普通的)📢</v>
+        <v>法官</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>hasten</v>
       </c>
       <c r="B26" t="str">
-        <v>Indian</v>
+        <v>/ˈheɪsn/</v>
       </c>
       <c r="C26" t="str">
-        <v>印度</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D26" t="str">
-        <v>Indian(印度)📢</v>
+        <v>加速</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>advanced</v>
       </c>
       <c r="B27" t="str">
-        <v>issue</v>
+        <v>/ədˈvænst/</v>
       </c>
       <c r="C27" t="str">
-        <v>发布</v>
+        <v>v./adj.</v>
       </c>
       <c r="D27" t="str">
-        <v>issue(发布)📢</v>
+        <v>先进的</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>jury</v>
       </c>
       <c r="B28" t="str">
-        <v>notebook</v>
+        <v>/ˈdʒʊri/</v>
       </c>
       <c r="C28" t="str">
-        <v>笔记本</v>
+        <v>n./adj.</v>
       </c>
       <c r="D28" t="str">
-        <v>notebook(笔记本)📢</v>
+        <v>陪审团</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>loosen</v>
       </c>
       <c r="B29" t="str">
-        <v>auto</v>
+        <v>/ˈluːsn/</v>
       </c>
       <c r="C29" t="str">
-        <v>汽车</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D29" t="str">
-        <v>auto(汽车)📢</v>
+        <v>松开</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>monitor</v>
       </c>
       <c r="B30" t="str">
-        <v>mean</v>
+        <v>/ˈmɑːnɪtər/</v>
       </c>
       <c r="C30" t="str">
-        <v>卑鄙的</v>
+        <v>n./vt.</v>
       </c>
       <c r="D30" t="str">
-        <v>mean(卑鄙的)📢</v>
+        <v>监控</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>population</v>
       </c>
       <c r="B31" t="str">
-        <v>foolish</v>
+        <v>/ˌpɑːpjuˈleɪʃn/</v>
       </c>
       <c r="C31" t="str">
-        <v>愚蠢的</v>
+        <v>n.</v>
       </c>
       <c r="D31" t="str">
-        <v>foolish(愚蠢的)📢</v>
+        <v>人口</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>dial</v>
       </c>
       <c r="B32" t="str">
-        <v>mean</v>
+        <v>/ˈdaɪəl/</v>
       </c>
       <c r="C32" t="str">
-        <v>意味着</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D32" t="str">
-        <v>mean(意味着)📢</v>
+        <v>电话</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>wire</v>
       </c>
       <c r="B33" t="str">
-        <v>folk</v>
+        <v>/ˈwaɪər/</v>
       </c>
       <c r="C33" t="str">
-        <v>民间</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D33" t="str">
-        <v>folk(民间)📢</v>
+        <v>电线</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>fog</v>
       </c>
       <c r="B34" t="str">
-        <v>former</v>
+        <v>/fɑːɡ/</v>
       </c>
       <c r="C34" t="str">
-        <v>以前的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D34" t="str">
-        <v>former(以前的)📢</v>
+        <v>雾</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>earth</v>
       </c>
       <c r="B35" t="str">
-        <v>judge</v>
+        <v>/ɜːrθ/</v>
       </c>
       <c r="C35" t="str">
-        <v>法官</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D35" t="str">
-        <v>judge(法官)📢</v>
+        <v>地球</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>fourth</v>
       </c>
       <c r="B36" t="str">
-        <v>hasten</v>
+        <v>/fɔːrθ/</v>
       </c>
       <c r="C36" t="str">
-        <v>加速</v>
+        <v>n./adj./num.</v>
       </c>
       <c r="D36" t="str">
-        <v>hasten(加速)📢</v>
+        <v>第四</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>rhythm</v>
       </c>
       <c r="B37" t="str">
-        <v>advanced</v>
+        <v>/ˈrɪðəm/</v>
       </c>
       <c r="C37" t="str">
-        <v>先进的</v>
+        <v>n.</v>
       </c>
       <c r="D37" t="str">
-        <v>advanced(先进的)📢</v>
+        <v>节奏</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>undo</v>
       </c>
       <c r="B38" t="str">
-        <v>jury</v>
+        <v>/ʌnˈduː/</v>
       </c>
       <c r="C38" t="str">
-        <v>陪审团</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D38" t="str">
-        <v>jury(陪审团)📢</v>
+        <v>解开</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>hydrogen</v>
       </c>
       <c r="B39" t="str">
-        <v>loosen</v>
+        <v>/ˈhaɪdrədʒən/</v>
       </c>
       <c r="C39" t="str">
-        <v>松开</v>
+        <v>n.</v>
       </c>
       <c r="D39" t="str">
-        <v>loosen(松开)📢</v>
+        <v>氢</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>mercy</v>
       </c>
       <c r="B40" t="str">
-        <v>monitor</v>
+        <v>/ˈmɜːrsi/</v>
       </c>
       <c r="C40" t="str">
-        <v>监控</v>
+        <v>n.</v>
       </c>
       <c r="D40" t="str">
-        <v>monitor(监控)📢</v>
+        <v>仁慈</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>anything</v>
       </c>
       <c r="B41" t="str">
-        <v>folk</v>
+        <v>/ˈeniθɪŋ/</v>
       </c>
       <c r="C41" t="str">
-        <v>民间</v>
+        <v>n./v./adv./pron.</v>
       </c>
       <c r="D41" t="str">
-        <v>folk(民间)📢</v>
+        <v>任何东西</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>spirit</v>
       </c>
       <c r="B42" t="str">
-        <v>small</v>
+        <v>/ˈspɪrɪt/</v>
       </c>
       <c r="C42" t="str">
-        <v>小的</v>
+        <v>n./vt.</v>
       </c>
       <c r="D42" t="str">
-        <v>small(小的)📢</v>
+        <v>精神</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>complete</v>
       </c>
       <c r="B43" t="str">
-        <v>population</v>
+        <v>/kəmˈpliːt/</v>
       </c>
       <c r="C43" t="str">
-        <v>人口</v>
+        <v>vt./adj.</v>
       </c>
       <c r="D43" t="str">
-        <v>population(人口)📢</v>
+        <v>完整的</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>distinction</v>
       </c>
       <c r="B44" t="str">
-        <v>Indian</v>
+        <v>/dɪˈstɪŋkʃn/</v>
       </c>
       <c r="C44" t="str">
-        <v>印度</v>
+        <v>n.</v>
       </c>
       <c r="D44" t="str">
-        <v>Indian(印度)📢</v>
+        <v>区别</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>queen</v>
       </c>
       <c r="B45" t="str">
-        <v>greenhouse</v>
+        <v>/kwiːn/</v>
       </c>
       <c r="C45" t="str">
-        <v>温室</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D45" t="str">
-        <v>greenhouse(温室)📢</v>
+        <v>女王</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>so</v>
       </c>
       <c r="B46" t="str">
-        <v>dial</v>
+        <v>/soʊ/</v>
       </c>
       <c r="C46" t="str">
-        <v>电话</v>
+        <v>n./v./adv./pron./conj.</v>
       </c>
       <c r="D46" t="str">
-        <v>dial(电话)📢</v>
+        <v>如此</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>means</v>
       </c>
       <c r="B47" t="str">
-        <v>wire</v>
+        <v>/miːnz/</v>
       </c>
       <c r="C47" t="str">
-        <v>电线</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D47" t="str">
-        <v>wire(电线)📢</v>
+        <v>手段</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>kiss</v>
       </c>
       <c r="B48" t="str">
-        <v>fog</v>
+        <v>/kɪs/</v>
       </c>
       <c r="C48" t="str">
-        <v>雾</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D48" t="str">
-        <v>fog(雾)📢</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49" t="str">
-        <v>card</v>
-      </c>
-      <c r="C49" t="str">
-        <v>卡片</v>
-      </c>
-      <c r="D49" t="str">
-        <v>card(卡片)📢</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="str">
-        <v>earth</v>
-      </c>
-      <c r="C50" t="str">
-        <v>地球</v>
-      </c>
-      <c r="D50" t="str">
-        <v>earth(地球)📢</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51" t="str">
-        <v>fourth</v>
-      </c>
-      <c r="C51" t="str">
-        <v>第四</v>
-      </c>
-      <c r="D51" t="str">
-        <v>fourth(第四)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>earth</v>
-      </c>
-      <c r="C52" t="str">
-        <v>地球</v>
-      </c>
-      <c r="D52" t="str">
-        <v>earth(地球)📢</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53">
-        <v>52</v>
-      </c>
-      <c r="B53" t="str">
-        <v>fourth</v>
-      </c>
-      <c r="C53" t="str">
-        <v>第四</v>
-      </c>
-      <c r="D53" t="str">
-        <v>fourth(第四)📢</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54">
-        <v>53</v>
-      </c>
-      <c r="B54" t="str">
-        <v>fourth</v>
-      </c>
-      <c r="C54" t="str">
-        <v>第四</v>
-      </c>
-      <c r="D54" t="str">
-        <v>fourth(第四)📢</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55">
-        <v>54</v>
-      </c>
-      <c r="B55" t="str">
-        <v>rhythm</v>
-      </c>
-      <c r="C55" t="str">
-        <v>节奏</v>
-      </c>
-      <c r="D55" t="str">
-        <v>rhythm(节奏)📢</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56">
-        <v>55</v>
-      </c>
-      <c r="B56" t="str">
-        <v>undo</v>
-      </c>
-      <c r="C56" t="str">
-        <v>解开</v>
-      </c>
-      <c r="D56" t="str">
-        <v>undo(解开)📢</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57">
-        <v>56</v>
-      </c>
-      <c r="B57" t="str">
-        <v>mean</v>
-      </c>
-      <c r="C57" t="str">
-        <v>想要</v>
-      </c>
-      <c r="D57" t="str">
-        <v>mean(想要)📢</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58">
-        <v>57</v>
-      </c>
-      <c r="B58" t="str">
-        <v>hydrogen</v>
-      </c>
-      <c r="C58" t="str">
-        <v>氢</v>
-      </c>
-      <c r="D58" t="str">
-        <v>hydrogen(氢)📢</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59">
-        <v>58</v>
-      </c>
-      <c r="B59" t="str">
-        <v>mercy</v>
-      </c>
-      <c r="C59" t="str">
-        <v>仁慈</v>
-      </c>
-      <c r="D59" t="str">
-        <v>mercy(仁慈)📢</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60">
-        <v>59</v>
-      </c>
-      <c r="B60" t="str">
-        <v>anything</v>
-      </c>
-      <c r="C60" t="str">
-        <v>任何东西</v>
-      </c>
-      <c r="D60" t="str">
-        <v>anything(任何东西)📢</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61">
-        <v>60</v>
-      </c>
-      <c r="B61" t="str">
-        <v>spirit</v>
-      </c>
-      <c r="C61" t="str">
-        <v>精神</v>
-      </c>
-      <c r="D61" t="str">
-        <v>spirit(精神)📢</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="str">
-        <v>complete</v>
-      </c>
-      <c r="C62" t="str">
-        <v>完整的</v>
-      </c>
-      <c r="D62" t="str">
-        <v>complete(完整的)📢</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63">
-        <v>62</v>
-      </c>
-      <c r="B63" t="str">
-        <v>judge</v>
-      </c>
-      <c r="C63" t="str">
-        <v>法官</v>
-      </c>
-      <c r="D63" t="str">
-        <v>judge(法官)📢</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64">
-        <v>63</v>
-      </c>
-      <c r="B64" t="str">
-        <v>distinction</v>
-      </c>
-      <c r="C64" t="str">
-        <v>区别</v>
-      </c>
-      <c r="D64" t="str">
-        <v>distinction(区别)📢</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65">
-        <v>64</v>
-      </c>
-      <c r="B65" t="str">
-        <v>charity</v>
-      </c>
-      <c r="C65" t="str">
-        <v>慈善</v>
-      </c>
-      <c r="D65" t="str">
-        <v>charity(慈善)📢</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66">
-        <v>65</v>
-      </c>
-      <c r="B66" t="str">
-        <v>queen</v>
-      </c>
-      <c r="C66" t="str">
-        <v>女王</v>
-      </c>
-      <c r="D66" t="str">
-        <v>queen(女王)📢</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67">
-        <v>66</v>
-      </c>
-      <c r="B67" t="str">
-        <v>advanced</v>
-      </c>
-      <c r="C67" t="str">
-        <v>先进的</v>
-      </c>
-      <c r="D67" t="str">
-        <v>advanced(先进的)📢</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="str">
-        <v>spirit</v>
-      </c>
-      <c r="C68" t="str">
-        <v>精神</v>
-      </c>
-      <c r="D68" t="str">
-        <v>spirit(精神)📢</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69">
-        <v>68</v>
-      </c>
-      <c r="B69" t="str">
-        <v>so</v>
-      </c>
-      <c r="C69" t="str">
-        <v>如此</v>
-      </c>
-      <c r="D69" t="str">
-        <v>so(如此)📢</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70">
-        <v>69</v>
-      </c>
-      <c r="B70" t="str">
-        <v>notebook</v>
-      </c>
-      <c r="C70" t="str">
-        <v>笔记本</v>
-      </c>
-      <c r="D70" t="str">
-        <v>notebook(笔记本)📢</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71">
-        <v>70</v>
-      </c>
-      <c r="B71" t="str">
-        <v>means</v>
-      </c>
-      <c r="C71" t="str">
-        <v>手段</v>
-      </c>
-      <c r="D71" t="str">
-        <v>means(手段)📢</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72">
-        <v>71</v>
-      </c>
-      <c r="B72" t="str">
-        <v>earth</v>
-      </c>
-      <c r="C72" t="str">
-        <v>地球</v>
-      </c>
-      <c r="D72" t="str">
-        <v>earth(地球)📢</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73">
-        <v>72</v>
-      </c>
-      <c r="B73" t="str">
-        <v>small</v>
-      </c>
-      <c r="C73" t="str">
-        <v>小的</v>
-      </c>
-      <c r="D73" t="str">
-        <v>small(小的)📢</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74">
-        <v>73</v>
-      </c>
-      <c r="B74" t="str">
-        <v>kiss</v>
-      </c>
-      <c r="C74" t="str">
         <v>亲吻</v>
-      </c>
-      <c r="D74" t="str">
-        <v>kiss(亲吻)📢</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75">
-        <v>74</v>
-      </c>
-      <c r="B75" t="str">
-        <v>notebook</v>
-      </c>
-      <c r="C75" t="str">
-        <v>笔记本</v>
-      </c>
-      <c r="D75" t="str">
-        <v>notebook(笔记本)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D75"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D48"/>
   </ignoredErrors>
 </worksheet>
 </file>